--- a/data/b2_primavera/B2 Primavera 07-2026.xlsx
+++ b/data/b2_primavera/B2 Primavera 07-2026.xlsx
@@ -4878,20 +4878,20 @@
     </row>
     <row r="2">
       <c r="A2" s="7" t="n">
-        <v>46208</v>
+        <v>46207</v>
       </c>
       <c r="B2" s="8" t="inlineStr">
         <is>
-          <t>Folha de pagamento</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>Salários do mês anterior</t>
+          <t>Coleta de resíduos (óleo e borra)</t>
         </is>
       </c>
       <c r="D2" s="16" t="n">
-        <v>57184.41</v>
+        <v>1366.06</v>
       </c>
     </row>
     <row r="3">
@@ -4900,52 +4900,52 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Folha de pagamento</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Salários do mês anterior</t>
         </is>
       </c>
       <c r="D3" s="17" t="n">
-        <v>2732.21</v>
+        <v>57013.65</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>46210</v>
+        <v>46208</v>
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>Tarifas bancárias</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D4" s="16" t="n">
-        <v>670.58</v>
+        <v>2881.23</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="12" t="n">
-        <v>46212</v>
+        <v>46210</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Seguro do posto</t>
+          <t>Manutenção preventiva das bombas</t>
         </is>
       </c>
       <c r="D5" s="17" t="n">
-        <v>1359.42</v>
+        <v>3590.92</v>
       </c>
     </row>
     <row r="6">
@@ -4990,16 +4990,16 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Coleta de resíduos (óleo e borra)</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D8" s="16" t="n">
-        <v>1496.45</v>
+        <v>4210.02</v>
       </c>
     </row>
     <row r="9">
@@ -5008,34 +5008,34 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Água e esgoto</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Conta de água</t>
         </is>
       </c>
       <c r="D9" s="17" t="n">
-        <v>4081.94</v>
+        <v>1207.01</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>46215</v>
+        <v>46218</v>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Água e esgoto</t>
+          <t>Energia elétrica</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Conta de água</t>
+          <t>Conta de energia</t>
         </is>
       </c>
       <c r="D10" s="16" t="n">
-        <v>1113.01</v>
+        <v>8922.17</v>
       </c>
     </row>
     <row r="11">
@@ -5044,70 +5044,70 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Energia elétrica</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Conta de energia</t>
+          <t>Placas, redes sociais e brindes</t>
         </is>
       </c>
       <c r="D11" s="17" t="n">
-        <v>8573.389999999999</v>
+        <v>3688.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>46218</v>
+        <v>46220</v>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Placas, redes sociais e brindes</t>
+          <t>Uniformes e EPI</t>
         </is>
       </c>
       <c r="D12" s="16" t="n">
-        <v>3708.7</v>
+        <v>1259.14</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="12" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Manutenção do compressor de ar</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D13" s="17" t="n">
-        <v>2370.59</v>
+        <v>3876.95</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Folha de pagamento</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Encargos (INSS e FGTS)</t>
         </is>
       </c>
       <c r="D14" s="16" t="n">
-        <v>3872.8</v>
+        <v>20285.61</v>
       </c>
     </row>
     <row r="15">
@@ -5116,34 +5116,34 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Folha de pagamento</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Encargos (INSS e FGTS)</t>
+          <t>Limpeza da caixa separadora</t>
         </is>
       </c>
       <c r="D15" s="17" t="n">
-        <v>20000.82</v>
+        <v>4322.22</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>46227</v>
+        <v>46229</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Troca de filtros das bombas</t>
+          <t>Monitoramento e alarme</t>
         </is>
       </c>
       <c r="D16" s="16" t="n">
-        <v>3630.99</v>
+        <v>1093.09</v>
       </c>
     </row>
     <row r="17">
@@ -5161,7 +5161,7 @@
         </is>
       </c>
       <c r="D17" s="17" t="n">
-        <v>3905.96</v>
+        <v>3940.16</v>
       </c>
     </row>
     <row r="18">
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="D18" s="16" t="n">
-        <v>2993.02</v>
+        <v>2907.26</v>
       </c>
     </row>
   </sheetData>
